--- a/T(C台)(P6-FU6)115918C-版本16.1130801(1131101更新)-範例.xlsx
+++ b/T(C台)(P6-FU6)115918C-版本16.1130801(1131101更新)-範例.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\95078\Desktop\高量採集自動收件\TSP_Excel_Batch_Unlock_V3\OUTPUT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E2011DF-8E02-4233-A07A-AA22DC0B2963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{01DD7166-B8E4-4E99-BF18-2A264628ABCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6284" yWindow="3665" windowWidth="18851" windowHeight="9766"/>
+    <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13667"/>
   </bookViews>
   <sheets>
     <sheet name="04" sheetId="102" r:id="rId1"/>
@@ -2038,7 +2038,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7EDE-420D-8A6D-1B8B57B24975}"/>
+              <c16:uniqueId val="{00000001-6C4F-4FFF-88BE-EE1C62EE3134}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2050,11 +2050,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1963553952"/>
+        <c:axId val="376245168"/>
         <c:axId val="1"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1963553952"/>
+        <c:axId val="376245168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.6"/>
@@ -2275,7 +2275,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1963553952"/>
+        <c:crossAx val="376245168"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2349,7 +2349,7 @@
         <xdr:cNvPr id="1805446" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE9EEEF5-89A0-4693-89AB-45D079E80C85}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2F40CC7-95E4-449C-9E72-0F329592803D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2387,7 +2387,7 @@
         <xdr:cNvPr id="3" name="文字方塊 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFD77710-1DB3-4C82-9A98-6200145319A8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31DCA626-010A-480C-9C56-B7024994E154}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2467,7 +2467,7 @@
         <xdr:cNvPr id="1805448" name="圖片 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B283DC7-E278-4D4F-A0DB-7E99072DDFDC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC2C7F1D-3BEA-408E-BB2E-08DA302204D4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2541,7 +2541,7 @@
         <xdr:cNvPr id="1805449" name="圖片 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3ED9F3AE-8910-490A-A142-3983CC6C4E00}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EE3B29B-E22A-4A29-B666-D0CE0016D141}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2615,7 +2615,7 @@
         <xdr:cNvPr id="6" name="文字方塊 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C06D480-C3CD-403C-93D6-1A362F35EB57}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFF9150B-39E2-430E-95E4-E49C023C6EE1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2695,7 +2695,7 @@
         <xdr:cNvPr id="1805451" name="圖片 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7A52DEF-E131-460F-9BC8-67E3F85B20F8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66643EEC-03F6-4DBF-9A6F-6824AC728DD9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2769,7 +2769,7 @@
         <xdr:cNvPr id="1805452" name="圖片 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48D5826C-F3FE-4B37-897F-B87B58CD5D1C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B103510F-F1DB-43C6-8D21-1373A1BBF1D8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
